--- a/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,10 +263,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare plan for patient or group</t>
-  </si>
-  <si>
-    <t>Describes the intention of how one or more practitioners intend to deliver care for a particular patient, group or community for a period of time, possibly limited to care for a specific condition or set of conditions.</t>
+    <t>特定照護目標下為一位患者或一群患者識別的活動、干預和結果計畫</t>
+  </si>
+  <si>
+    <t>描述為實現一個或多個目標而將為一位患者(或一群患者)進行的活動的計畫，包括診斷、監測、評估、治療、藥物治療、追蹤等。</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -292,13 +292,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>不重複的 ID 用以識別儲存在特定 FHIR Server 中的 CarePlan 紀錄，通常又稱為邏輯性 ID。</t>
+  </si>
+  <si>
+    <t>resource 的邏輯 ID，在 resource 的 URL 中使用。一旦指定，這個值永遠不會改變。</t>
+  </si>
+  <si>
+    <t>一個 resource 使用新增操作(create operation)提交給伺服器時，此 resource 沒有 id，它的 id 在 resource 被創建後由伺器分配/指定。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -311,10 +311,10 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>此 CarePlan Resource 的 metadata</t>
+  </si>
+  <si>
+    <t>關於 resource 的 metadata。這是由基礎建設維護的內容。內容的更改可能並不總是與 resource 的版本更改相關聯。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -331,13 +331,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
+  </si>
+  <si>
+    <t>宣告這套規則限制了內容只能被有限的交易夥伴所理解。這從本質上限制了資料的長期有用性。然而，現有的健康生態體系高度分裂，還沒有準備好以普遍可計算的方式定義、收集和交換資料。只要有可能，實作者和/或規範編寫者應該避免使用這個資料項目。通常在使用時，此 URL 是對 IG 的參照，此 IG 將這些特殊規則與其他 profiles、value sets 等一起定義為其敘述的一部分。</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -350,19 +350,22 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>用以表述 CarePlan Resource 內容的語言</t>
+  </si>
+  <si>
+    <t>編寫此 resource 的語言</t>
+  </si>
+  <si>
+    <t>提供語言是為了支援索引和可存取性(通常，文字表述轉語音等服務使用此語言標籤)。html lanuage tag 適用於此敘述。resource 上的語言標籤可用於指定從 resource 中的資料所產成的其他表述之語言。不是所有的內容都必須使用此語言。不應該假定 Resource.language 自動適用於敘述。如果指定語言，它也應該被指定在 html 中的 div 資料項目(關於 xml:lang 和 html lang 屬性之間的關係，見 HTML5 中的規則)。</t>
+  </si>
+  <si>
+    <t>zh-TW</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>人類語言；鼓勵使用 CommonLanguages 代碼表中的代碼，但不強制一定要使用此代碼表，你也可使用其他代碼表的代碼或單純以文字表示。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -382,13 +385,13 @@
 </t>
   </si>
   <si>
-    <t>CarePlan Resource之內容摘要以供人閱讀</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>CarePlan Resource 之內容摘要以供人閱讀</t>
+  </si>
+  <si>
+    <t>人可讀的敘述，包含 resource 的摘要，可用於向人表述 resource 的內容。敘述不需要對所有的結構化資料進行編碼，但需要包含足夠的細節使人在閱讀敘述時理解「臨床安全性」。resource 定義有哪些內容應該在敘述中表示，以確保臨床安全。</t>
+  </si>
+  <si>
+    <t>內嵌(contained)的 resource 沒有敘述，非內嵌(contained)的 resource 則 **建議應該(SHOULD)** 有敘述。有時 resource 可能只有文字表述，很少或沒有額外的結構化資料(只要滿足所有 minOccurs=1 的資料項目)。這可能出現在舊系統的資料，當資訊以 「文字表述區塊(text blob)」的形式被取得，或者文字表述是原始輸入或說明，而編碼資訊稍後再添加。</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -465,7 +468,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Constrained value set of narrative statuses.</t>
+    <t>敘述狀態的受限值集。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/narrative-status</t>
@@ -484,7 +487,7 @@
 </t>
   </si>
   <si>
-    <t>Limited xhtml content</t>
+    <t>有限的 xhtml 內容</t>
   </si>
   <si>
     <t>The actual narrative content, a stripped down version of XHTML.</t>
@@ -582,7 +585,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -624,10 +627,13 @@
 </t>
   </si>
   <si>
-    <t>Fulfills CarePlan</t>
-  </si>
-  <si>
-    <t>A care plan that is fulfilled in whole or in part by this care plan.</t>
+    <t>履行或延伸的照護計畫</t>
+  </si>
+  <si>
+    <t>識別此照護計畫所建立的父計畫。</t>
+  </si>
+  <si>
+    <t>參照可以是相對的、絕對的或內部的。</t>
   </si>
   <si>
     <t>Allows tracing of the care plan and tracking whether proposals/recommendations were acted upon.</t>
@@ -643,13 +649,10 @@
 </t>
   </si>
   <si>
-    <t>CarePlan replaced by this CarePlan</t>
-  </si>
-  <si>
-    <t>Completed or terminated care plan whose function is taken by this new care plan.</t>
-  </si>
-  <si>
-    <t>The replacement could be because the initial care plan was immediately rejected (due to an issue) or because the previous care plan was completed, but the need for the action described by the care plan remains ongoing.</t>
+    <t>被此計畫取代的照護計畫</t>
+  </si>
+  <si>
+    <t>識別被此照護計畫所取代的照護計畫。</t>
   </si>
   <si>
     <t>Allows tracing the continuation of a therapy or administrative process instantiated through multiple care plans.</t>
@@ -661,26 +664,25 @@
     <t>CarePlan.partOf</t>
   </si>
   <si>
-    <t>Part of referenced CarePlan</t>
-  </si>
-  <si>
-    <t>A larger care plan of which this particular care plan is a component or step.</t>
-  </si>
-  <si>
-    <t>Each care plan is an independent request, such that having a care plan be part of another care plan can cause issues with cascading statuses.  As such, this element is still being discussed.</t>
+    <t>作為父照護計畫的一部分</t>
+  </si>
+  <si>
+    <t>此照護計畫是另一個照護計畫的一部分。例如，專門針對骨折修復或糖尿病控制的計畫可能是出院護理計畫的一部分。</t>
   </si>
   <si>
     <t>CarePlan.status</t>
   </si>
   <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
-  </si>
-  <si>
-    <t>The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the care plan.
-This element is labeled as a modifier because the status contains the code entered-in-error that marks the plan as not currently valid.</t>
+    <t>照護計畫目前的狀態</t>
+  </si>
+  <si>
+    <t>指明照護計畫是否正在執行中、表示未來意向或現在已成為歷史記錄。</t>
+  </si>
+  <si>
+    <t>可以在 [[event.html#statemachine | 事件模式]] 文件中找到一個標準的狀態轉換圖。「未知」不代表「其他」狀態 - 必須使用其中一個已定義的狀態，「未知」用於表示不確定當前狀態。</t>
+  </si>
+  <si>
+    <t>指出計畫是否正在實施、代表未來意圖或是現在的歷史記錄。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-status</t>
@@ -701,10 +703,10 @@
     <t>CarePlan.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+    <t>照護計畫的意圖</t>
+  </si>
+  <si>
+    <t>表示與照護計畫相關的權威性/意向性程度。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -716,7 +718,7 @@
     <t>plan</t>
   </si>
   <si>
-    <t>Codes indicating the degree of authority/intentionality associated with a care plan</t>
+    <t>表示與照護計畫相關的權威性/意向性程度的代碼</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-intent</t>
@@ -732,16 +734,16 @@
 </t>
   </si>
   <si>
-    <t>Type of plan</t>
-  </si>
-  <si>
-    <t>Type of plan.</t>
+    <t>照護計畫的類型</t>
+  </si>
+  <si>
+    <t>照護計畫的類型。</t>
   </si>
   <si>
     <t>There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
   </si>
   <si>
-    <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g., "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
+    <t>識別這是什麼「種類」的計畫，以支援多個共存計畫之間的區分；例如：「居家健康」、「精神科」、「氣喘」、「疾病管理」、「保健計畫」等。</t>
   </si>
   <si>
     <t>example</t>
@@ -750,7 +752,7 @@
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -764,6 +766,9 @@
   </si>
   <si>
     <t>AssessPlan</t>
+  </si>
+  <si>
+    <t>評估計畫</t>
   </si>
   <si>
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
@@ -815,13 +820,13 @@
 </t>
   </si>
   <si>
-    <t>Who the care plan is for</t>
-  </si>
-  <si>
-    <t>Who care plan is for.</t>
-  </si>
-  <si>
-    <t>Identifies the patient or group whose intended care is described by the plan.</t>
+    <t>照護計畫的對象</t>
+  </si>
+  <si>
+    <t>照護計畫是為了誰。</t>
+  </si>
+  <si>
+    <t>識別計畫描述其意圖照護的病人或群體。</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -843,13 +848,13 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
+    <t>與此照護計畫相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此照護計畫是在哪個就醫情境產生的。</t>
+  </si>
+  <si>
+    <t>參照可以是相對的、絕對的或內部的。注意：如果 Encounter 參照是一個 Episode of Care 的一部分，則此資料點不足以隱含建立關聯。</t>
   </si>
   <si>
     <t>Request.context</t>
@@ -987,13 +992,10 @@
 </t>
   </si>
   <si>
-    <t>Who is the designated responsible party</t>
-  </si>
-  <si>
-    <t>When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
-  </si>
-  <si>
-    <t>The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
+    <t>照護計畫的作者</t>
+  </si>
+  <si>
+    <t>負責建立照護計畫內容的個人或組織。</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1005,13 +1007,10 @@
     <t>CarePlan.contributor</t>
   </si>
   <si>
-    <t>Who provided the content of the care plan</t>
-  </si>
-  <si>
-    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
-  </si>
-  <si>
-    <t>Collaborative care plans may have multiple contributors.</t>
+    <t>對計畫提供資訊的人員</t>
+  </si>
+  <si>
+    <t>對照護計畫的建立提供資訊的個人或組織，但不對照護計畫負責。</t>
   </si>
   <si>
     <t>CarePlan.careTeam</t>
@@ -1021,10 +1020,10 @@
 </t>
   </si>
   <si>
-    <t>Who's involved in plan?</t>
-  </si>
-  <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
+    <t>執行照護工作的團隊</t>
+  </si>
+  <si>
+    <t>確定負責執行此照護計畫的照護團隊。</t>
   </si>
   <si>
     <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
@@ -1043,13 +1042,10 @@
 </t>
   </si>
   <si>
-    <t>Health issues this plan addresses</t>
-  </si>
-  <si>
-    <t>Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
-  </si>
-  <si>
-    <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
+    <t>本計畫處理的健康問題</t>
+  </si>
+  <si>
+    <t>本照護計畫試圖解決的健康問題(例如：疾病、病情、問題)。</t>
   </si>
   <si>
     <t>Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
@@ -1092,7 +1088,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1179,13 +1175,13 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1239,14 +1235,10 @@
 </t>
   </si>
   <si>
-    <t>Activity details defined in specific resource</t>
-  </si>
-  <si>
-    <t>The details of the proposed activity represented in a specific resource.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  -The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
+    <t>照護行動的明細</t>
+  </si>
+  <si>
+    <t>包含照護計畫之照護行動(診斷、治療等)明細的 request/request-like 資源。</t>
   </si>
   <si>
     <t>Details in a form consistent with other applications and contexts of use.</t>
@@ -1333,7 +1325,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1367,7 +1359,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1394,7 +1386,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1407,10 +1399,10 @@
 </t>
   </si>
   <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+    <t>為何需要此行動</t>
+  </si>
+  <si>
+    <t>指出為何此行動是此照護計畫的一部分。</t>
   </si>
   <si>
     <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
@@ -1541,13 +1533,10 @@
 </t>
   </si>
   <si>
-    <t>Where it should happen</t>
-  </si>
-  <si>
-    <t>Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
-  </si>
-  <si>
-    <t>May reference a specific clinical location or may identify a type of location.</t>
+    <t>行動發生的地點</t>
+  </si>
+  <si>
+    <t>預期要執行此行動的地點。</t>
   </si>
   <si>
     <t>Helps in planning of activity.</t>
@@ -1566,13 +1555,10 @@
 </t>
   </si>
   <si>
-    <t>Who will be responsible?</t>
-  </si>
-  <si>
-    <t>Identifies who's expected to be involved in the activity.</t>
-  </si>
-  <si>
-    <t>A performer MAY also be a participant in the care plan.</t>
+    <t>執行或提供此行動的人員</t>
+  </si>
+  <si>
+    <t>確定預期要執行此行動的特定人員或組織。</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1588,7 +1574,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>What is to be administered/supplied</t>
@@ -1600,7 +1586,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1619,6 +1605,12 @@
 </t>
   </si>
   <si>
+    <t>物料/主題/產品資訊要參照的資源</t>
+  </si>
+  <si>
+    <t>辨識行動所涉及的物料/主題/產品。</t>
+  </si>
+  <si>
     <t>CarePlan.activity.detail.dailyAmount</t>
   </si>
   <si>
@@ -1626,7 +1618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2670,7 +2662,7 @@
         <v>20</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>20</v>
@@ -2682,13 +2674,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2706,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2735,14 +2727,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2761,16 +2753,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2820,7 +2812,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2838,7 +2830,7 @@
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -2849,10 +2841,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2875,13 +2867,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2932,7 +2924,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2950,7 +2942,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2961,14 +2953,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2987,16 +2979,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3034,19 +3026,19 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3058,13 +3050,13 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>20</v>
@@ -3075,10 +3067,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3104,10 +3096,10 @@
         <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3134,13 +3126,13 @@
         <v>20</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>20</v>
@@ -3158,7 +3150,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>87</v>
@@ -3176,7 +3168,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>20</v>
@@ -3187,10 +3179,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3213,16 +3205,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3272,7 +3264,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>87</v>
@@ -3284,13 +3276,13 @@
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -3301,14 +3293,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3327,16 +3319,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3386,7 +3378,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3404,7 +3396,7 @@
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -3415,14 +3407,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3441,16 +3433,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3500,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3512,13 +3504,13 @@
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>20</v>
@@ -3529,14 +3521,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3555,19 +3547,19 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3616,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3628,13 +3620,13 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
@@ -3645,10 +3637,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3671,19 +3663,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3732,7 +3724,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3747,24 +3739,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3787,13 +3779,13 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3844,7 +3836,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3859,10 +3851,10 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3873,10 +3865,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3902,13 +3894,13 @@
         <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3958,7 +3950,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3973,10 +3965,10 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3987,14 +3979,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4013,17 +4005,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4072,7 +4066,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4087,7 +4081,7 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
@@ -4101,14 +4095,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4127,19 +4121,19 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4188,7 +4182,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4203,7 +4197,7 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
@@ -4217,10 +4211,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4243,16 +4237,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4302,7 +4296,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4369,7 +4363,7 @@
         <v>212</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4394,13 +4388,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4433,24 +4427,24 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4476,16 +4470,16 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4495,7 +4489,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4510,13 +4504,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4534,7 +4528,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -4549,7 +4543,7 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -4563,10 +4557,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4589,19 +4583,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4626,29 +4620,29 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4669,7 +4663,7 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4677,13 +4671,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
@@ -4705,19 +4699,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4727,7 +4721,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4742,13 +4736,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4766,7 +4760,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4787,7 +4781,7 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4795,10 +4789,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4821,13 +4815,13 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4878,7 +4872,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4907,10 +4901,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4933,17 +4927,17 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4992,7 +4986,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5013,7 +5007,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -5021,14 +5015,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5047,17 +5041,17 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5106,7 +5100,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>87</v>
@@ -5121,24 +5115,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5161,16 +5155,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5220,7 +5214,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5235,28 +5229,28 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5275,19 +5269,19 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5336,7 +5330,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5351,24 +5345,24 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5391,13 +5385,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5448,7 +5442,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5466,7 +5460,7 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -5477,14 +5471,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5503,16 +5497,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5550,19 +5544,19 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5574,13 +5568,13 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5591,10 +5585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5617,16 +5611,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5676,7 +5670,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5685,7 +5679,7 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
@@ -5694,21 +5688,21 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5731,23 +5725,23 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>20</v>
@@ -5792,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5801,7 +5795,7 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
@@ -5810,25 +5804,25 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5847,13 +5841,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5904,7 +5898,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5919,13 +5913,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5933,10 +5927,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5959,16 +5953,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6018,7 +6012,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6033,13 +6027,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6047,10 +6041,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6073,16 +6067,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6132,7 +6126,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6195,7 +6189,9 @@
       <c r="M37" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>322</v>
       </c>
@@ -6310,10 +6306,10 @@
         <v>328</v>
       </c>
       <c r="N38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6377,24 +6373,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6417,19 +6413,19 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6478,7 +6474,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6493,7 +6489,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6507,10 +6503,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6533,19 +6529,19 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6594,7 +6590,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6612,21 +6608,21 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6649,17 +6645,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6708,7 +6704,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6720,13 +6716,13 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6737,10 +6733,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6763,13 +6759,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6820,7 +6816,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6838,7 +6834,7 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6849,14 +6845,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6875,16 +6871,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6934,7 +6930,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6946,13 +6942,13 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
@@ -6963,14 +6959,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6989,19 +6985,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7050,7 +7046,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7062,13 +7058,13 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -7079,10 +7075,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7105,16 +7101,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7140,14 +7136,14 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7164,7 +7160,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7193,10 +7189,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7219,19 +7215,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7280,7 +7276,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7295,10 +7291,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7309,10 +7305,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7335,19 +7331,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7396,7 +7392,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7414,21 +7410,21 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7451,19 +7447,19 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7512,7 +7508,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7521,16 +7517,16 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7541,10 +7537,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7567,17 +7563,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7626,7 +7622,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7635,7 +7631,7 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -7644,7 +7640,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7655,10 +7651,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7681,13 +7677,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7738,7 +7734,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7756,7 +7752,7 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7767,10 +7763,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7793,13 +7789,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7838,17 +7834,17 @@
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7860,7 +7856,7 @@
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7877,13 +7873,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>20</v>
@@ -7905,13 +7901,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7962,7 +7958,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7971,10 +7967,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7991,14 +7987,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8017,19 +8013,19 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8078,7 +8074,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8090,13 +8086,13 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -8107,10 +8103,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8136,14 +8132,14 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8168,13 +8164,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8192,7 +8188,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8210,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -8221,10 +8217,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8247,17 +8243,17 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8306,7 +8302,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8321,10 +8317,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8335,10 +8331,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8364,16 +8360,16 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8422,7 +8418,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8437,10 +8433,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8451,10 +8447,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8477,19 +8473,19 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8514,13 +8510,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8538,7 +8534,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8553,24 +8549,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8593,16 +8589,16 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8628,13 +8624,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8652,7 +8648,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8667,7 +8663,7 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
@@ -8681,10 +8677,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8707,16 +8703,16 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8766,7 +8762,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8781,7 +8777,7 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
@@ -8795,10 +8791,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8821,17 +8817,17 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8880,7 +8876,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8898,7 +8894,7 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -8909,10 +8905,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8938,16 +8934,16 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -8972,13 +8968,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8996,7 +8992,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>87</v>
@@ -9011,24 +9007,24 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>459</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9051,16 +9047,16 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9110,7 +9106,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9125,7 +9121,7 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -9139,10 +9135,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9165,26 +9161,26 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="O63" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="s" s="2">
-        <v>471</v>
-      </c>
       <c r="R63" t="s" s="2">
         <v>20</v>
       </c>
@@ -9228,7 +9224,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9243,10 +9239,10 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
@@ -9257,10 +9253,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9283,17 +9279,17 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9330,17 +9326,17 @@
         <v>20</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9355,27 +9351,27 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>20</v>
@@ -9397,17 +9393,17 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9456,7 +9452,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9471,24 +9467,24 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9511,19 +9507,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="N66" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9572,7 +9568,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9590,21 +9586,21 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9627,19 +9623,19 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>496</v>
+        <v>197</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9688,7 +9684,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9703,24 +9699,24 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9743,13 +9739,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9776,29 +9772,29 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9816,24 +9812,24 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>20</v>
@@ -9855,15 +9851,17 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9912,7 +9910,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9930,25 +9928,25 @@
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9967,17 +9965,17 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10026,7 +10024,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10044,21 +10042,21 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10081,13 +10079,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10138,7 +10136,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10156,21 +10154,21 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10193,13 +10191,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10250,7 +10248,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10268,21 +10266,21 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10305,17 +10303,17 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10364,7 +10362,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10379,16 +10377,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
+++ b/docs/StructureDefinition-LTC-CarePlan-CS100.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
